--- a/docs/downloads/04/tbl_class_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_ambatoharanana.xlsx
@@ -397,12 +397,6 @@
           <t>Primaire</t>
         </is>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>66.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -420,12 +414,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>33.3</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -443,12 +431,6 @@
           <t>Primaire</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,12 +448,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>57.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -532,14 +508,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>25</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -555,14 +525,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -578,14 +542,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>25</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -670,14 +628,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>0.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -739,7 +691,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
@@ -808,14 +760,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D20">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E20">
-        <v>17.4</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="21">
@@ -826,19 +778,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E21">
-        <v>1.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="22">
@@ -854,14 +806,8 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>21</v>
-      </c>
-      <c r="E22">
-        <v>53.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -877,14 +823,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D23">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>43.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="24">
@@ -895,19 +841,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -923,14 +863,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D25">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="E25">
-        <v>12.9</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="26">
@@ -946,14 +886,8 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>185</v>
-      </c>
-      <c r="E26">
-        <v>85.3</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -969,14 +903,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E27">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
